--- a/Configs/GameConfig/Datas/rank.xlsx
+++ b/Configs/GameConfig/Datas/rank.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>rankName</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -516,14 +516,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,7 +565,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
         <v>0</v>
       </c>
@@ -608,7 +599,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>1</v>
       </c>
@@ -643,7 +633,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
         <v>2</v>
       </c>
@@ -678,7 +667,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
         <v>3</v>
       </c>
@@ -713,7 +701,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
         <v>4</v>
       </c>
@@ -748,7 +735,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>5</v>
       </c>
@@ -783,7 +769,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
         <v>6</v>
       </c>
@@ -818,7 +803,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
         <v>7</v>
       </c>
@@ -853,7 +837,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
         <v>8</v>
       </c>
@@ -888,7 +871,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
         <v>9</v>
       </c>
@@ -923,7 +905,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
         <v>10</v>
       </c>
@@ -958,7 +939,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
         <v>11</v>
       </c>
@@ -993,7 +973,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
         <v>12</v>
       </c>
@@ -1028,7 +1007,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
         <v>13</v>
       </c>
@@ -1063,7 +1041,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
         <v>14</v>
       </c>
@@ -1098,7 +1075,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
         <v>15</v>
       </c>
@@ -1133,7 +1109,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
         <v>16</v>
       </c>
@@ -1168,7 +1143,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
         <v>17</v>
       </c>
@@ -1203,7 +1177,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
         <v>18</v>
       </c>
@@ -1238,7 +1211,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
         <v>19</v>
       </c>
@@ -1273,7 +1245,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
         <v>20</v>
       </c>
@@ -1308,7 +1279,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
         <v>21</v>
       </c>
@@ -1343,7 +1313,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
         <v>22</v>
       </c>
@@ -1378,7 +1347,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
         <v>23</v>
       </c>
@@ -1413,7 +1381,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
         <v>24</v>
       </c>
@@ -1448,7 +1415,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
         <v>25</v>
       </c>
@@ -1483,7 +1449,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
         <v>26</v>
       </c>
@@ -1518,7 +1483,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
         <v>27</v>
       </c>
@@ -1553,7 +1517,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
         <v>28</v>
       </c>
@@ -1588,7 +1551,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
         <v>29</v>
       </c>
@@ -1623,7 +1585,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
         <v>30</v>
       </c>
@@ -1658,7 +1619,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
         <v>31</v>
       </c>
@@ -1693,7 +1653,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
         <v>32</v>
       </c>
@@ -1728,7 +1687,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
         <v>33</v>
       </c>
@@ -1763,7 +1721,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
         <v>34</v>
       </c>
@@ -1798,7 +1755,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
         <v>35</v>
       </c>
@@ -1833,7 +1789,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
         <v>36</v>
       </c>
@@ -1868,7 +1823,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
         <v>37</v>
       </c>
@@ -1903,7 +1857,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
         <v>38</v>
       </c>
@@ -1938,7 +1891,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
         <v>39</v>
       </c>
@@ -1973,7 +1925,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
         <v>40</v>
       </c>
@@ -2008,7 +1959,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
         <v>41</v>
       </c>
@@ -2043,7 +1993,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
         <v>42</v>
       </c>
@@ -2078,7 +2027,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
         <v>43</v>
       </c>
@@ -2113,7 +2061,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
         <v>44</v>
       </c>
@@ -2148,7 +2095,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
         <v>45</v>
       </c>
@@ -2183,7 +2129,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
         <v>46</v>
       </c>
@@ -2218,7 +2163,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
         <v>47</v>
       </c>
@@ -2253,7 +2197,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
         <v>48</v>
       </c>
@@ -2288,7 +2231,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
         <v>49</v>
       </c>
@@ -2323,7 +2265,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
         <v>50</v>
       </c>
@@ -2358,7 +2299,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
         <v>51</v>
       </c>
@@ -2393,7 +2333,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
         <v>52</v>
       </c>
@@ -2428,7 +2367,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
         <v>53</v>
       </c>
